--- a/MaHH.xlsx
+++ b/MaHH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Works 2\IT\GITHUB\UpSSE_render\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F639B7A-EB94-415B-A2BC-38798CE2BDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C267F28-E5F0-4458-9847-F3B4446C4E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1154C90-8187-4C9D-8DDB-7618463980C9}"/>
   </bookViews>
@@ -1013,10 +1013,10 @@
     <t>Xăng dầu</t>
   </si>
   <si>
-    <t>Xăng E10 RON95 Mức 3</t>
-  </si>
-  <si>
     <t>HH051</t>
+  </si>
+  <si>
+    <t>Xăng E10 RON 95 Mức 3</t>
   </si>
 </sst>
 </file>
@@ -4287,13 +4287,13 @@
     </row>
     <row r="162" spans="1:4" ht="31.5" x14ac:dyDescent="0.15">
       <c r="A162" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>325</v>
